--- a/InputData/geoeng/ERWD/Enhanced Rock Weathering Data.xlsx
+++ b/InputData/geoeng/ERWD/Enhanced Rock Weathering Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\geoeng\ERWD\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-india\InputData\geoeng\ERWD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98AAF143-D02D-4BA9-A61C-1E4CE8806B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1663131-2D1B-484D-8E2E-548C58323707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -138,9 +138,6 @@
     <t>Supplemental information, Figure 9</t>
   </si>
   <si>
-    <t>We report the US specific cost and potential.</t>
-  </si>
-  <si>
     <t>USA representative cost per ton</t>
   </si>
   <si>
@@ -178,6 +175,9 @@
   </si>
   <si>
     <t>a very large scale-up of capacity and transportation logistics.</t>
+  </si>
+  <si>
+    <t>We report the India specific cost and potential.</t>
   </si>
 </sst>
 </file>
@@ -606,17 +606,17 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -659,27 +659,27 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -699,7 +699,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -709,7 +709,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27">
         <v>947817</v>
@@ -732,15 +732,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1">
-        <v>150</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2">
         <v>138</v>
@@ -748,7 +748,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3">
         <v>700</v>
@@ -756,7 +756,7 @@
     </row>
     <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B4">
         <v>0.66</v>
@@ -2257,127 +2257,127 @@
       </c>
       <c r="B2">
         <f>('Fuhrman data'!B1+'Fuhrman data'!B2)*About!A25</f>
-        <v>255.4878733902346</v>
+        <v>171.21235959831694</v>
       </c>
       <c r="C2">
         <f>($AF$2-$B$2)/COUNT($C$1:$AF$1)+B2</f>
-        <v>251.4071643013628</v>
+        <v>167.13165050944514</v>
       </c>
       <c r="D2">
         <f t="shared" ref="D2:AE2" si="0">($AF$2-$B$2)/COUNT($C$1:$AF$1)+C2</f>
-        <v>247.326455212491</v>
+        <v>163.05094142057334</v>
       </c>
       <c r="E2">
         <f t="shared" si="0"/>
-        <v>243.2457461236192</v>
+        <v>158.97023233170154</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>239.1650370347474</v>
+        <v>154.88952324282974</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>235.0843279458756</v>
+        <v>150.80881415395794</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>231.0036188570038</v>
+        <v>146.72810506508614</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>226.922909768132</v>
+        <v>142.64739597621434</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>222.8422006792602</v>
+        <v>138.56668688734254</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>218.7614915903884</v>
+        <v>134.48597779847074</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>214.6807825015166</v>
+        <v>130.40526870959894</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>210.6000734126448</v>
+        <v>126.32455962072714</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>206.519364323773</v>
+        <v>122.24385053185534</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>202.4386552349012</v>
+        <v>118.16314144298354</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>198.35794614602941</v>
+        <v>114.08243235411175</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>194.27723705715761</v>
+        <v>110.00172326523995</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>190.19652796828581</v>
+        <v>105.92101417636815</v>
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>186.11581887941401</v>
+        <v>101.84030508749635</v>
       </c>
       <c r="T2">
         <f t="shared" si="0"/>
-        <v>182.03510979054221</v>
+        <v>97.759595998624548</v>
       </c>
       <c r="U2">
         <f t="shared" si="0"/>
-        <v>177.95440070167041</v>
+        <v>93.678886909752748</v>
       </c>
       <c r="V2">
         <f t="shared" si="0"/>
-        <v>173.87369161279861</v>
+        <v>89.598177820880949</v>
       </c>
       <c r="W2">
         <f t="shared" si="0"/>
-        <v>169.79298252392681</v>
+        <v>85.517468732009149</v>
       </c>
       <c r="X2">
         <f t="shared" si="0"/>
-        <v>165.71227343505501</v>
+        <v>81.43675964313735</v>
       </c>
       <c r="Y2">
         <f t="shared" si="0"/>
-        <v>161.63156434618321</v>
+        <v>77.356050554265551</v>
       </c>
       <c r="Z2">
         <f t="shared" si="0"/>
-        <v>157.55085525731141</v>
+        <v>73.275341465393751</v>
       </c>
       <c r="AA2">
         <f t="shared" si="0"/>
-        <v>153.47014616843961</v>
+        <v>69.194632376521952</v>
       </c>
       <c r="AB2">
         <f t="shared" si="0"/>
-        <v>149.38943707956781</v>
+        <v>65.113923287650152</v>
       </c>
       <c r="AC2">
         <f t="shared" si="0"/>
-        <v>145.30872799069601</v>
+        <v>61.033214198778353</v>
       </c>
       <c r="AD2">
         <f t="shared" si="0"/>
-        <v>141.22801890182421</v>
+        <v>56.952505109906554</v>
       </c>
       <c r="AE2">
         <f t="shared" si="0"/>
-        <v>137.14730981295241</v>
+        <v>52.871796021034754</v>
       </c>
       <c r="AF2">
         <f>'Fuhrman data'!B1*About!A25</f>
-        <v>133.06660072408053</v>
+        <v>48.791086932162855</v>
       </c>
     </row>
   </sheetData>
